--- a/fuction_ensemble/redes-ensemble-s/mse_sup_ensemble_100/25_model/25_model_24_4_24.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/mse_sup_ensemble_100/25_model/25_model_24_4_24.xlsx
@@ -452,10 +452,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
         <v>1.759168997909792</v>
@@ -466,10 +466,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="B3" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="C3" t="n">
         <v>1.904544178635538</v>
@@ -494,10 +494,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="B5" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="C5" t="n">
         <v>0.6951161619240627</v>
@@ -508,10 +508,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>2.560174814827988</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>1.521226903575671</v>
@@ -536,10 +536,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="B8" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="C8" t="n">
         <v>1.666602084301417</v>
@@ -564,10 +564,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="B10" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="C10" t="n">
         <v>0.4571740675899418</v>
@@ -578,10 +578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>2.322232720493867</v>
@@ -592,10 +592,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
         <v>2.816739155750824</v>
@@ -606,10 +606,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="B13" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="C13" t="n">
         <v>2.96211433647657</v>
@@ -634,10 +634,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="B15" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="C15" t="n">
         <v>1.752686319765095</v>
@@ -648,10 +648,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>3.617744972669021</v>
@@ -662,10 +662,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>2.502536279404641</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="B18" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="C18" t="n">
         <v>2.647911460130388</v>
@@ -704,10 +704,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="B20" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="C20" t="n">
         <v>1.438483443418912</v>
@@ -718,10 +718,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
         <v>3.303542096322838</v>
@@ -732,10 +732,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
         <v>2.473616686300074</v>
@@ -746,10 +746,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="B23" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="C23" t="n">
         <v>2.618991867025821</v>
@@ -774,10 +774,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="B25" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="C25" t="n">
         <v>1.409563850314345</v>
@@ -788,10 +788,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>3.274622503218271</v>
